--- a/app_notas_uis.xlsx
+++ b/app_notas_uis.xlsx
@@ -48,13 +48,24 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF980000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF9900FF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF660000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF351C75"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -72,18 +83,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF980000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF9900FF"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
+      <color rgb="FF351C75"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -135,13 +135,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
@@ -156,35 +156,35 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -518,7 +518,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="5" t="str">
+      <c r="H1" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEKS")</f>
         <v>ALEKS</v>
       </c>
@@ -585,11 +585,11 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="13">
+      <c r="G2" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8100000000000005)</f>
         <v>4.81</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
@@ -613,7 +613,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="N2" s="17">
+      <c r="N2" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -621,7 +621,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P2" s="18">
+      <c r="P2" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6905)</f>
         <v>2.6905</v>
       </c>
@@ -656,11 +656,11 @@
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="13">
+      <c r="G3" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6799999999999997)</f>
         <v>3.68</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
       </c>
@@ -684,7 +684,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7000000000000002)</f>
         <v>1.7</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -692,7 +692,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.654)</f>
         <v>1.654</v>
       </c>
@@ -727,11 +727,11 @@
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5700000000000003)</f>
         <v>3.57</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
         <v>1.3</v>
       </c>
@@ -755,7 +755,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -763,7 +763,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4000000000000001)</f>
         <v>1.4</v>
       </c>
-      <c r="P4" s="18">
+      <c r="P4" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4485000000000001)</f>
         <v>1.4485</v>
       </c>
@@ -798,11 +798,11 @@
       </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="13">
+      <c r="G5" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
         <v>0.1</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -826,7 +826,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -834,7 +834,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="18">
+      <c r="P5" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.025000000000000005)</f>
         <v>0.025</v>
       </c>
@@ -869,11 +869,11 @@
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -897,7 +897,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -905,7 +905,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="18">
+      <c r="P6" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4600000000000002)</f>
         <v>1.46</v>
       </c>
@@ -940,11 +940,11 @@
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.22)</f>
         <v>1.22</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -968,7 +968,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -976,7 +976,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="18">
+      <c r="P7" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.601)</f>
         <v>0.601</v>
       </c>
@@ -1011,11 +1011,11 @@
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7199999999999998)</f>
         <v>2.72</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
         <v>1.1</v>
       </c>
@@ -1039,7 +1039,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1047,7 +1047,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
         <v>0.4</v>
       </c>
-      <c r="P8" s="18">
+      <c r="P8" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4060000000000001)</f>
         <v>1.406</v>
       </c>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.63)</f>
         <v>2.63</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
       </c>
@@ -1110,7 +1110,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.15)</f>
         <v>2.15</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -1118,7 +1118,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7000000000000001)</f>
         <v>0.7</v>
       </c>
-      <c r="P9" s="18">
+      <c r="P9" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8614999999999999)</f>
         <v>0.8615</v>
       </c>
@@ -1153,11 +1153,11 @@
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7199999999999998)</f>
         <v>2.72</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
         <v>1.2</v>
       </c>
@@ -1181,7 +1181,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1189,7 +1189,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.30000000000000004)</f>
         <v>0.3</v>
       </c>
-      <c r="P10" s="18">
+      <c r="P10" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2560000000000002)</f>
         <v>2.256</v>
       </c>
@@ -1224,11 +1224,11 @@
       </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.47)</f>
         <v>3.47</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
@@ -1252,7 +1252,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1260,7 +1260,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.15000000000000002)</f>
         <v>0.15</v>
       </c>
-      <c r="P11" s="18">
+      <c r="P11" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7735)</f>
         <v>1.7735</v>
       </c>
@@ -1295,11 +1295,11 @@
       </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.470000000000001)</f>
         <v>4.47</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
@@ -1323,7 +1323,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1000000000000005)</f>
         <v>4.1</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1331,7 +1331,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="P12" s="18">
+      <c r="P12" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5835)</f>
         <v>2.5835</v>
       </c>
@@ -1366,11 +1366,11 @@
       </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
         <v>0.4</v>
       </c>
@@ -1394,7 +1394,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -1402,7 +1402,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="18">
+      <c r="P13" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.44999999999999996)</f>
         <v>0.45</v>
       </c>
@@ -1437,11 +1437,11 @@
       </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.65)</f>
         <v>3.65</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
@@ -1465,7 +1465,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3000000000000003)</f>
         <v>3.3</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1473,7 +1473,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P14" s="18">
+      <c r="P14" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8125000000000004)</f>
         <v>1.8125</v>
       </c>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -1536,7 +1536,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1544,7 +1544,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="18">
+      <c r="P15" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.46)</f>
         <v>1.46</v>
       </c>
@@ -1579,11 +1579,11 @@
       </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
         <v>0.4</v>
       </c>
@@ -1607,7 +1607,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -1615,7 +1615,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.15000000000000002)</f>
         <v>0.15</v>
       </c>
-      <c r="P16" s="18">
+      <c r="P16" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9000000000000001)</f>
         <v>0.9</v>
       </c>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.48)</f>
         <v>2.48</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
         <v>0.9</v>
       </c>
@@ -1678,7 +1678,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1686,7 +1686,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.15000000000000002)</f>
         <v>0.15</v>
       </c>
-      <c r="P17" s="18">
+      <c r="P17" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6540000000000001)</f>
         <v>1.654</v>
       </c>
@@ -1721,11 +1721,11 @@
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="13">
+      <c r="G18" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.13)</f>
         <v>4.13</v>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
@@ -1749,7 +1749,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="N18" s="17">
+      <c r="N18" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1757,7 +1757,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.55)</f>
         <v>1.55</v>
       </c>
-      <c r="P18" s="18">
+      <c r="P18" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0065)</f>
         <v>2.0065</v>
       </c>
@@ -1792,11 +1792,11 @@
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="13">
+      <c r="G19" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.25)</f>
         <v>4.25</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
@@ -1820,7 +1820,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.45)</f>
         <v>4.45</v>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1828,7 +1828,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9000000000000004)</f>
         <v>3.9</v>
       </c>
-      <c r="P19" s="18">
+      <c r="P19" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6524999999999999)</f>
         <v>1.6525</v>
       </c>
@@ -1863,11 +1863,11 @@
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="13">
+      <c r="G20" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.779999999999999)</f>
         <v>4.78</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
@@ -1891,7 +1891,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1899,7 +1899,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P20" s="18">
+      <c r="P20" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5090000000000003)</f>
         <v>2.509</v>
       </c>
@@ -1934,11 +1934,11 @@
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.68)</f>
         <v>4.68</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
@@ -1962,7 +1962,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.65)</f>
         <v>4.65</v>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -1970,7 +1970,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P21" s="18">
+      <c r="P21" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.564)</f>
         <v>2.564</v>
       </c>
@@ -2000,16 +2000,16 @@
         <v>3.1</v>
       </c>
       <c r="D22" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
-        <v>0.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
-      </c>
-      <c r="H22" s="15">
+      <c r="G22" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="H22" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
         <v>0.8</v>
       </c>
@@ -2033,17 +2033,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="17">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+      <c r="N22" s="18">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="O22" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.30000000000000004)</f>
         <v>0.3</v>
       </c>
-      <c r="P22" s="18">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8800000000000001)</f>
-        <v>0.88</v>
+      <c r="P22" s="21">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9700000000000002)</f>
+        <v>0.97</v>
       </c>
       <c r="Q22" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262174.0)</f>
@@ -2076,11 +2076,11 @@
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
       </c>
@@ -2104,7 +2104,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2112,7 +2112,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.30000000000000004)</f>
         <v>0.3</v>
       </c>
-      <c r="P23" s="18">
+      <c r="P23" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.91)</f>
         <v>1.91</v>
       </c>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="13">
+      <c r="G24" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.52)</f>
         <v>2.52</v>
       </c>
-      <c r="H24" s="15">
+      <c r="H24" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
@@ -2175,7 +2175,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="17">
+      <c r="N24" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2183,7 +2183,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6500000000000001)</f>
         <v>1.65</v>
       </c>
-      <c r="P24" s="18">
+      <c r="P24" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7359999999999998)</f>
         <v>1.736</v>
       </c>
@@ -2218,11 +2218,11 @@
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="13">
+      <c r="G25" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.680000000000001)</f>
         <v>4.68</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
@@ -2246,7 +2246,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.85)</f>
         <v>3.85</v>
       </c>
-      <c r="N25" s="17">
+      <c r="N25" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2254,7 +2254,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9500000000000001)</f>
         <v>0.95</v>
       </c>
-      <c r="P25" s="18">
+      <c r="P25" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2840000000000003)</f>
         <v>2.284</v>
       </c>
@@ -2289,11 +2289,11 @@
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="13">
+      <c r="G26" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.37)</f>
         <v>4.37</v>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
@@ -2317,7 +2317,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.45)</f>
         <v>4.45</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2325,7 +2325,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P26" s="18">
+      <c r="P26" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2485000000000004)</f>
         <v>2.2485</v>
       </c>
@@ -2360,11 +2360,11 @@
       </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="13">
+      <c r="G27" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2700000000000005)</f>
         <v>4.27</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
@@ -2388,7 +2388,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.45)</f>
         <v>4.45</v>
       </c>
-      <c r="N27" s="17">
+      <c r="N27" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2396,7 +2396,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.15000000000000002)</f>
         <v>0.15</v>
       </c>
-      <c r="P27" s="18">
+      <c r="P27" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0435)</f>
         <v>2.0435</v>
       </c>
@@ -2431,11 +2431,11 @@
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="13">
+      <c r="G28" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3200000000000003)</f>
         <v>3.32</v>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
@@ -2459,7 +2459,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
         <v>1.6</v>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2467,7 +2467,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P28" s="18">
+      <c r="P28" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3659999999999997)</f>
         <v>2.366</v>
       </c>
@@ -2502,11 +2502,11 @@
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="13">
+      <c r="G29" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3100000000000005)</f>
         <v>4.31</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
@@ -2530,7 +2530,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.75)</f>
         <v>4.75</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2538,7 +2538,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P29" s="18">
+      <c r="P29" s="21">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0655)</f>
         <v>2.0655</v>
       </c>
@@ -2573,11 +2573,11 @@
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="13">
+      <c r="G30" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.54)</f>
         <v>4.54</v>
       </c>
-      <c r="H30" s="15">
+      <c r="H30" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
@@ -2601,7 +2601,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.45)</f>
         <v>4.45</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2609,7 +2609,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4000000000000001)</f>
         <v>1.4</v>
       </c>
-      <c r="P30" s="23">
+      <c r="P30" s="22">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.597)</f>
         <v>2.597</v>
       </c>
@@ -2637,11 +2637,11 @@
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.48)</f>
         <v>4.48</v>
       </c>
-      <c r="H31" s="15">
+      <c r="H31" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
@@ -2665,7 +2665,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.85)</f>
         <v>3.85</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2673,7 +2673,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8500000000000005)</f>
         <v>4.85</v>
       </c>
-      <c r="P31" s="23">
+      <c r="P31" s="22">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.134)</f>
         <v>2.134</v>
       </c>
@@ -2701,11 +2701,11 @@
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="13">
+      <c r="G32" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.53)</f>
         <v>3.53</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
       </c>
@@ -2729,7 +2729,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="N32" s="17">
+      <c r="N32" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2737,7 +2737,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.30000000000000004)</f>
         <v>0.3</v>
       </c>
-      <c r="P32" s="23">
+      <c r="P32" s="22">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9465000000000001)</f>
         <v>0.9465</v>
       </c>
@@ -2765,11 +2765,11 @@
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="13">
+      <c r="G33" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.430000000000001)</f>
         <v>4.43</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
@@ -2793,7 +2793,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
         <v>4.55</v>
       </c>
-      <c r="N33" s="17">
+      <c r="N33" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2801,7 +2801,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="P33" s="23">
+      <c r="P33" s="22">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3114999999999999)</f>
         <v>1.3115</v>
       </c>
@@ -2829,11 +2829,11 @@
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="13">
+      <c r="G34" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7600000000000002)</f>
         <v>3.76</v>
       </c>
-      <c r="H34" s="15">
+      <c r="H34" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
         <v>2.3</v>
       </c>
@@ -2857,7 +2857,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1000000000000005)</f>
         <v>4.1</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="18">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -2865,7 +2865,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="P34" s="23">
+      <c r="P34" s="22">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.458)</f>
         <v>1.458</v>
       </c>
@@ -2956,7 +2956,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="6" t="str">
+      <c r="H1" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTOR")</f>
         <v>TUTOR</v>
       </c>
@@ -2976,7 +2976,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Q2")</f>
         <v>Q2</v>
       </c>
-      <c r="M1" s="1"/>
+      <c r="M1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Tr2")</f>
+        <v>Tr2</v>
+      </c>
       <c r="N1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FINAL")</f>
         <v>FINAL</v>
@@ -3010,14 +3013,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="D2" s="11"/>
+      <c r="D2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="12">
+      <c r="G2" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="H2" s="14"/>
+      <c r="H2" s="20"/>
       <c r="I2" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -3034,10 +3040,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9749999999999999)</f>
-        <v>0.975</v>
+      <c r="M2" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N2" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.825)</f>
+        <v>1.825</v>
       </c>
       <c r="O2" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262798.0)</f>
@@ -3068,14 +3077,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D3" s="11"/>
+      <c r="D3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12">
+      <c r="G3" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="H3" s="14"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -3092,10 +3104,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.15)</f>
-        <v>1.15</v>
+      <c r="M3" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N3" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="O3" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261614.0)</f>
@@ -3126,14 +3141,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12">
+      <c r="G4" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="H4" s="14"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -3150,10 +3168,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
-        <v>1.21</v>
+      <c r="M4" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N4" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.335)</f>
+        <v>2.335</v>
       </c>
       <c r="O4" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263262.0)</f>
@@ -3184,14 +3205,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12">
+      <c r="G5" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -3208,10 +3232,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.165)</f>
-        <v>1.165</v>
+      <c r="M5" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N5" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2399999999999998)</f>
+        <v>2.24</v>
       </c>
       <c r="O5" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262846.0)</f>
@@ -3242,14 +3269,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12">
+      <c r="G6" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="20"/>
       <c r="I6" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -3266,10 +3296,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
+      <c r="M6" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N6" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="O6" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2253791.0)</f>
@@ -3300,14 +3333,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12">
+      <c r="G7" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="20"/>
       <c r="I7" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -3324,10 +3360,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.17)</f>
-        <v>1.17</v>
+      <c r="M7" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N7" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.17)</f>
+        <v>2.17</v>
       </c>
       <c r="O7" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262988.0)</f>
@@ -3358,14 +3397,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12">
+      <c r="G8" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="20"/>
       <c r="I8" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -3382,8 +3424,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="16">
+      <c r="M8" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -3416,14 +3461,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12">
+      <c r="G9" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="H9" s="14"/>
+      <c r="H9" s="20"/>
       <c r="I9" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
@@ -3440,10 +3488,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
-        <v>1.1</v>
+      <c r="M9" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N9" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.35)</f>
+        <v>2.35</v>
       </c>
       <c r="O9" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262852.0)</f>
@@ -3474,14 +3525,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12">
+      <c r="G10" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="H10" s="14"/>
+      <c r="H10" s="20"/>
       <c r="I10" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -3498,10 +3552,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.95)</f>
-        <v>0.95</v>
+      <c r="M10" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1500000000000001)</f>
+        <v>1.15</v>
       </c>
       <c r="O10" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263024.0)</f>
@@ -3532,14 +3589,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12">
+      <c r="G11" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="H11" s="14"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
@@ -3556,10 +3616,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0050000000000001)</f>
-        <v>1.005</v>
+      <c r="M11" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N11" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.08)</f>
+        <v>2.08</v>
       </c>
       <c r="O11" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262408.0)</f>
@@ -3590,14 +3653,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12">
+      <c r="G12" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="H12" s="14"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
@@ -3614,10 +3680,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8700000000000001)</f>
-        <v>0.87</v>
+      <c r="M12" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N12" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.495)</f>
+        <v>1.495</v>
       </c>
       <c r="O12" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262903.0)</f>
@@ -3648,14 +3717,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12">
+      <c r="G13" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -3672,10 +3744,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.08)</f>
-        <v>1.08</v>
+      <c r="M13" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N13" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.93)</f>
+        <v>1.93</v>
       </c>
       <c r="O13" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263076.0)</f>
@@ -3706,14 +3781,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12">
+      <c r="G14" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -3730,10 +3808,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.07)</f>
-        <v>1.07</v>
+      <c r="M14" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N14" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.62)</f>
+        <v>1.62</v>
       </c>
       <c r="O14" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263291.0)</f>
@@ -3764,14 +3845,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12">
+      <c r="G15" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -3788,10 +3872,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.12)</f>
-        <v>1.12</v>
+      <c r="M15" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N15" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.87)</f>
+        <v>1.87</v>
       </c>
       <c r="O15" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262833.0)</f>
@@ -3822,14 +3909,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
+        <v>0.3</v>
+      </c>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12">
+      <c r="G16" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
       </c>
-      <c r="H16" s="14"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -3846,10 +3936,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.93)</f>
-        <v>0.93</v>
+      <c r="M16" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.005)</f>
+        <v>1.005</v>
       </c>
       <c r="O16" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262797.0)</f>
@@ -3880,14 +3973,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12">
+      <c r="G17" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
         <v>1.6</v>
@@ -3904,10 +4000,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.845)</f>
-        <v>0.845</v>
+      <c r="M17" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N17" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.595)</f>
+        <v>1.595</v>
       </c>
       <c r="O17" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263036.0)</f>
@@ -3938,14 +4037,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
         <v>2.8</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12">
+      <c r="G18" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -3962,10 +4064,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
-        <v>0.81</v>
+      <c r="M18" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N18" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8849999999999998)</f>
+        <v>1.885</v>
       </c>
       <c r="O18" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262913.0)</f>
@@ -3996,14 +4101,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="H19" s="14"/>
+      <c r="G19" s="19">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H19" s="20"/>
       <c r="I19" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -4020,10 +4128,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.25)</f>
-        <v>1.25</v>
+      <c r="M19" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N19" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.375)</f>
+        <v>2.375</v>
       </c>
       <c r="O19" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263115.0)</f>
@@ -4054,14 +4165,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12">
+      <c r="G20" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="H20" s="14"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
@@ -4078,10 +4192,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
-        <v>1.155</v>
+      <c r="M20" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N20" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.355)</f>
+        <v>2.355</v>
       </c>
       <c r="O20" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263124.0)</f>
@@ -4112,14 +4229,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="H21" s="14"/>
+      <c r="G21" s="19">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H21" s="20"/>
       <c r="I21" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -4136,10 +4256,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.25)</f>
-        <v>1.25</v>
+      <c r="M21" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N21" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.375)</f>
+        <v>2.375</v>
       </c>
       <c r="O21" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262915.0)</f>
@@ -4170,14 +4293,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12">
+      <c r="G22" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -4194,10 +4320,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
-        <v>1.1</v>
+      <c r="M22" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N22" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.05)</f>
+        <v>2.05</v>
       </c>
       <c r="O22" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2261867.0)</f>
@@ -4228,14 +4357,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="H23" s="14"/>
+      <c r="G23" s="19">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H23" s="20"/>
       <c r="I23" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -4252,10 +4384,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.25)</f>
-        <v>1.25</v>
+      <c r="M23" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N23" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="O23" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262941.0)</f>
@@ -4286,14 +4421,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="D24" s="11"/>
+      <c r="D24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12">
+      <c r="G24" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="H24" s="14"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -4310,10 +4448,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.025)</f>
-        <v>1.025</v>
+      <c r="M24" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N24" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0999999999999996)</f>
+        <v>2.1</v>
       </c>
       <c r="O24" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262847.0)</f>
@@ -4344,14 +4485,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12">
+      <c r="G25" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="H25" s="14"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
@@ -4368,10 +4512,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.12)</f>
-        <v>1.12</v>
+      <c r="M25" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N25" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7950000000000002)</f>
+        <v>1.795</v>
       </c>
       <c r="O25" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262882.0)</f>
@@ -4402,14 +4549,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12">
+      <c r="G26" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="H26" s="14"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -4426,10 +4576,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.93)</f>
-        <v>0.93</v>
+      <c r="M26" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N26" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5550000000000002)</f>
+        <v>1.555</v>
       </c>
       <c r="O26" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263137.0)</f>
@@ -4460,14 +4613,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12">
+      <c r="G27" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="H27" s="14"/>
+      <c r="H27" s="20"/>
       <c r="I27" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -4484,10 +4640,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.75)</f>
-        <v>0.75</v>
+      <c r="M27" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N27" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="O27" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263289.0)</f>
@@ -4518,14 +4677,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="D28" s="11"/>
+      <c r="D28" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12">
+      <c r="G28" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="H28" s="14"/>
+      <c r="H28" s="20"/>
       <c r="I28" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -4542,10 +4704,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M28" s="9"/>
-      <c r="N28" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.15)</f>
-        <v>1.15</v>
+      <c r="M28" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N28" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.275)</f>
+        <v>2.275</v>
       </c>
       <c r="O28" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263073.0)</f>
@@ -4576,14 +4741,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="D29" s="11"/>
+      <c r="D29" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="12">
+      <c r="G29" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="H29" s="14"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -4600,10 +4768,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M29" s="9"/>
-      <c r="N29" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9199999999999999)</f>
-        <v>0.92</v>
+      <c r="M29" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N29" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.745)</f>
+        <v>1.745</v>
       </c>
       <c r="O29" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262868.0)</f>
@@ -4634,14 +4805,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="D30" s="11"/>
+      <c r="D30" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="12">
+      <c r="G30" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="H30" s="14"/>
+      <c r="H30" s="20"/>
       <c r="I30" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -4658,10 +4832,13 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M30" s="9"/>
-      <c r="N30" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.87)</f>
-        <v>0.87</v>
+      <c r="M30" s="9">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="N30" s="17">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8199999999999998)</f>
+        <v>1.82</v>
       </c>
       <c r="O30" s="10">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2243227.0)</f>
@@ -8627,7 +8804,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTOR")</f>
         <v>TUTOR</v>
       </c>
-      <c r="H1" s="7" t="str">
+      <c r="H1" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALEKS")</f>
         <v>ALEKS</v>
       </c>
@@ -8701,12 +8878,12 @@
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20">
+      <c r="G2" s="12"/>
+      <c r="H2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1500000000000004)</f>
         <v>3.15</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
@@ -8731,11 +8908,11 @@
         <v>5</v>
       </c>
       <c r="O2" s="9"/>
-      <c r="P2" s="16">
+      <c r="P2" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8150000000000001)</f>
         <v>0.815</v>
       </c>
-      <c r="Q2" s="21">
+      <c r="Q2" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262336.0)</f>
         <v>2262336</v>
       </c>
@@ -8776,12 +8953,12 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20">
+      <c r="G3" s="12"/>
+      <c r="H3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -8806,11 +8983,11 @@
         <v>5</v>
       </c>
       <c r="O3" s="9"/>
-      <c r="P3" s="16">
+      <c r="P3" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262712.0)</f>
         <v>2262712</v>
       </c>
@@ -8851,12 +9028,12 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="20">
+      <c r="G4" s="12"/>
+      <c r="H4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
         <v>4.55</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -8881,11 +9058,11 @@
         <v>5</v>
       </c>
       <c r="O4" s="9"/>
-      <c r="P4" s="16">
+      <c r="P4" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.155)</f>
         <v>1.155</v>
       </c>
-      <c r="Q4" s="21">
+      <c r="Q4" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262739.0)</f>
         <v>2262739</v>
       </c>
@@ -8926,12 +9103,12 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20">
+      <c r="G5" s="12"/>
+      <c r="H5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.800000000000001)</f>
         <v>4.8</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -8956,11 +9133,11 @@
         <v>5</v>
       </c>
       <c r="O5" s="9"/>
-      <c r="P5" s="16">
+      <c r="P5" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.48)</f>
         <v>1.48</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="Q5" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262501.0)</f>
         <v>2262501</v>
       </c>
@@ -9001,12 +9178,12 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="20">
+      <c r="G6" s="12"/>
+      <c r="H6" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -9031,11 +9208,11 @@
         <v>5</v>
       </c>
       <c r="O6" s="9"/>
-      <c r="P6" s="16">
+      <c r="P6" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.06)</f>
         <v>1.06</v>
       </c>
-      <c r="Q6" s="21">
+      <c r="Q6" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262759.0)</f>
         <v>2262759</v>
       </c>
@@ -9076,12 +9253,12 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="20">
+      <c r="G7" s="12"/>
+      <c r="H7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.05)</f>
         <v>4.05</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.67)</f>
         <v>3.67</v>
       </c>
@@ -9106,11 +9283,11 @@
         <v>5</v>
       </c>
       <c r="O7" s="9"/>
-      <c r="P7" s="16">
+      <c r="P7" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.405)</f>
         <v>1.405</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="Q7" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2260624.0)</f>
         <v>2260624</v>
       </c>
@@ -9151,12 +9328,12 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="20">
+      <c r="G8" s="12"/>
+      <c r="H8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1000000000000005)</f>
         <v>4.1</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -9181,11 +9358,11 @@
         <v>5</v>
       </c>
       <c r="O8" s="9"/>
-      <c r="P8" s="16">
+      <c r="P8" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4100000000000001)</f>
         <v>1.41</v>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262444.0)</f>
         <v>2262444</v>
       </c>
@@ -9226,12 +9403,12 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20">
+      <c r="G9" s="12"/>
+      <c r="H9" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1500000000000004)</f>
         <v>3.15</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -9256,11 +9433,11 @@
         <v>5</v>
       </c>
       <c r="O9" s="9"/>
-      <c r="P9" s="16">
+      <c r="P9" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2550000000000001)</f>
         <v>1.255</v>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262438.0)</f>
         <v>2262438</v>
       </c>
@@ -9301,12 +9478,12 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="20">
+      <c r="G10" s="12"/>
+      <c r="H10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.45)</f>
         <v>4.45</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -9331,11 +9508,11 @@
         <v>5</v>
       </c>
       <c r="O10" s="9"/>
-      <c r="P10" s="16">
+      <c r="P10" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.445)</f>
         <v>1.445</v>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262746.0)</f>
         <v>2262746</v>
       </c>
@@ -9376,12 +9553,12 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20">
+      <c r="G11" s="12"/>
+      <c r="H11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
         <v>4.55</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -9406,11 +9583,11 @@
         <v>5</v>
       </c>
       <c r="O11" s="9"/>
-      <c r="P11" s="16">
+      <c r="P11" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.215)</f>
         <v>1.215</v>
       </c>
-      <c r="Q11" s="21">
+      <c r="Q11" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262454.0)</f>
         <v>2262454</v>
       </c>
@@ -9451,12 +9628,12 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20">
+      <c r="G12" s="12"/>
+      <c r="H12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -9481,11 +9658,11 @@
         <v>5</v>
       </c>
       <c r="O12" s="9"/>
-      <c r="P12" s="16">
+      <c r="P12" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.25)</f>
         <v>1.25</v>
       </c>
-      <c r="Q12" s="21">
+      <c r="Q12" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2263866.0)</f>
         <v>2263866</v>
       </c>
@@ -9526,12 +9703,12 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="20">
+      <c r="G13" s="12"/>
+      <c r="H13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1000000000000005)</f>
         <v>4.1</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.67)</f>
         <v>3.67</v>
       </c>
@@ -9556,11 +9733,11 @@
         <v>5</v>
       </c>
       <c r="O13" s="9"/>
-      <c r="P13" s="16">
+      <c r="P13" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2900000000000003)</f>
         <v>1.29</v>
       </c>
-      <c r="Q13" s="21">
+      <c r="Q13" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262973.0)</f>
         <v>2262973</v>
       </c>
@@ -9601,12 +9778,12 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20">
+      <c r="G14" s="12"/>
+      <c r="H14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.33)</f>
         <v>4.33</v>
       </c>
@@ -9631,11 +9808,11 @@
         <v>5</v>
       </c>
       <c r="O14" s="9"/>
-      <c r="P14" s="16">
+      <c r="P14" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.04)</f>
         <v>1.04</v>
       </c>
-      <c r="Q14" s="21">
+      <c r="Q14" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262338.0)</f>
         <v>2262338</v>
       </c>
@@ -9676,12 +9853,12 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20">
+      <c r="G15" s="12"/>
+      <c r="H15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.75)</f>
         <v>3.75</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -9706,11 +9883,11 @@
         <v>5</v>
       </c>
       <c r="O15" s="9"/>
-      <c r="P15" s="16">
+      <c r="P15" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.135)</f>
         <v>1.135</v>
       </c>
-      <c r="Q15" s="21">
+      <c r="Q15" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262977.0)</f>
         <v>2262977</v>
       </c>
@@ -9751,12 +9928,12 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20">
+      <c r="G16" s="12"/>
+      <c r="H16" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -9781,11 +9958,11 @@
         <v>5</v>
       </c>
       <c r="O16" s="9"/>
-      <c r="P16" s="16">
+      <c r="P16" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.82)</f>
         <v>0.82</v>
       </c>
-      <c r="Q16" s="21">
+      <c r="Q16" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262574.0)</f>
         <v>2262574</v>
       </c>
@@ -9826,12 +10003,12 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20">
+      <c r="G17" s="12"/>
+      <c r="H17" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.67)</f>
         <v>3.67</v>
       </c>
@@ -9856,11 +10033,11 @@
         <v>5</v>
       </c>
       <c r="O17" s="9"/>
-      <c r="P17" s="16">
+      <c r="P17" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.15)</f>
         <v>1.15</v>
       </c>
-      <c r="Q17" s="21">
+      <c r="Q17" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262343.0)</f>
         <v>2262343</v>
       </c>
@@ -9901,12 +10078,12 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20">
+      <c r="G18" s="12"/>
+      <c r="H18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.45)</f>
         <v>2.45</v>
       </c>
-      <c r="I18" s="21">
+      <c r="I18" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -9931,11 +10108,11 @@
         <v>5</v>
       </c>
       <c r="O18" s="9"/>
-      <c r="P18" s="16">
+      <c r="P18" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9650000000000001)</f>
         <v>0.965</v>
       </c>
-      <c r="Q18" s="21">
+      <c r="Q18" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262867.0)</f>
         <v>2262867</v>
       </c>
@@ -9976,12 +10153,12 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20">
+      <c r="G19" s="12"/>
+      <c r="H19" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
         <v>2.9</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.83)</f>
         <v>4.83</v>
       </c>
@@ -10006,11 +10183,11 @@
         <v>5</v>
       </c>
       <c r="O19" s="9"/>
-      <c r="P19" s="16">
+      <c r="P19" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.29)</f>
         <v>1.29</v>
       </c>
-      <c r="Q19" s="21">
+      <c r="Q19" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262650.0)</f>
         <v>2262650</v>
       </c>
@@ -10051,12 +10228,12 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20">
+      <c r="G20" s="12"/>
+      <c r="H20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.75)</f>
         <v>4.75</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -10081,11 +10258,11 @@
         <v>5</v>
       </c>
       <c r="O20" s="9"/>
-      <c r="P20" s="16">
+      <c r="P20" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.195)</f>
         <v>1.195</v>
       </c>
-      <c r="Q20" s="21">
+      <c r="Q20" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262876.0)</f>
         <v>2262876</v>
       </c>
@@ -10126,12 +10303,12 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20">
+      <c r="G21" s="12"/>
+      <c r="H21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -10156,11 +10333,11 @@
         <v>5</v>
       </c>
       <c r="O21" s="9"/>
-      <c r="P21" s="16">
+      <c r="P21" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="Q21" s="21">
+      <c r="Q21" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262361.0)</f>
         <v>2262361</v>
       </c>
@@ -10201,12 +10378,12 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20">
+      <c r="G22" s="12"/>
+      <c r="H22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1500000000000004)</f>
         <v>3.15</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.33)</f>
         <v>3.33</v>
       </c>
@@ -10231,11 +10408,11 @@
         <v>5</v>
       </c>
       <c r="O22" s="9"/>
-      <c r="P22" s="16">
+      <c r="P22" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8150000000000001)</f>
         <v>0.815</v>
       </c>
-      <c r="Q22" s="21">
+      <c r="Q22" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262613.0)</f>
         <v>2262613</v>
       </c>
@@ -10276,12 +10453,12 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20">
+      <c r="G23" s="12"/>
+      <c r="H23" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4000000000000004)</f>
         <v>2.4</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -10306,11 +10483,11 @@
         <v>5</v>
       </c>
       <c r="O23" s="9"/>
-      <c r="P23" s="16">
+      <c r="P23" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.24)</f>
         <v>1.24</v>
       </c>
-      <c r="Q23" s="21">
+      <c r="Q23" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262932.0)</f>
         <v>2262932</v>
       </c>
@@ -10351,12 +10528,12 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20">
+      <c r="G24" s="12"/>
+      <c r="H24" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3000000000000003)</f>
         <v>3.3</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -10381,11 +10558,11 @@
         <v>5</v>
       </c>
       <c r="O24" s="9"/>
-      <c r="P24" s="16">
+      <c r="P24" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.15)</f>
         <v>1.15</v>
       </c>
-      <c r="Q24" s="21">
+      <c r="Q24" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262645.0)</f>
         <v>2262645</v>
       </c>
@@ -10426,12 +10603,12 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="20">
+      <c r="G25" s="12"/>
+      <c r="H25" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.17)</f>
         <v>4.17</v>
       </c>
@@ -10456,11 +10633,11 @@
         <v>5</v>
       </c>
       <c r="O25" s="9"/>
-      <c r="P25" s="16">
+      <c r="P25" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.36)</f>
         <v>1.36</v>
       </c>
-      <c r="Q25" s="21">
+      <c r="Q25" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262884.0)</f>
         <v>2262884</v>
       </c>
@@ -10501,12 +10678,12 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="20">
+      <c r="G26" s="12"/>
+      <c r="H26" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.95)</f>
         <v>2.95</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -10531,11 +10708,11 @@
         <v>5</v>
       </c>
       <c r="O26" s="9"/>
-      <c r="P26" s="16">
+      <c r="P26" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.195)</f>
         <v>1.195</v>
       </c>
-      <c r="Q26" s="21">
+      <c r="Q26" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2250720.0)</f>
         <v>2250720</v>
       </c>
@@ -10576,12 +10753,12 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="20">
+      <c r="G27" s="12"/>
+      <c r="H27" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.95)</f>
         <v>2.95</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -10606,11 +10783,11 @@
         <v>5</v>
       </c>
       <c r="O27" s="9"/>
-      <c r="P27" s="16">
+      <c r="P27" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8950000000000001)</f>
         <v>0.895</v>
       </c>
-      <c r="Q27" s="21">
+      <c r="Q27" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262794.0)</f>
         <v>2262794</v>
       </c>
@@ -10651,12 +10828,12 @@
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="20">
+      <c r="G28" s="12"/>
+      <c r="H28" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.33)</f>
         <v>4.33</v>
       </c>
@@ -10681,11 +10858,11 @@
         <v>5</v>
       </c>
       <c r="O28" s="9"/>
-      <c r="P28" s="16">
+      <c r="P28" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.44)</f>
         <v>1.44</v>
       </c>
-      <c r="Q28" s="21">
+      <c r="Q28" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262621.0)</f>
         <v>2262621</v>
       </c>
@@ -10726,12 +10903,12 @@
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="20">
+      <c r="G29" s="12"/>
+      <c r="H29" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
         <v>4.55</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -10756,11 +10933,11 @@
         <v>0</v>
       </c>
       <c r="O29" s="9"/>
-      <c r="P29" s="16">
+      <c r="P29" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.355)</f>
         <v>1.355</v>
       </c>
-      <c r="Q29" s="21">
+      <c r="Q29" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262862.0)</f>
         <v>2262862</v>
       </c>
@@ -10801,12 +10978,12 @@
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20">
+      <c r="G30" s="12"/>
+      <c r="H30" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.55)</f>
         <v>4.55</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
@@ -10831,11 +11008,11 @@
         <v>5</v>
       </c>
       <c r="O30" s="9"/>
-      <c r="P30" s="16">
+      <c r="P30" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.455)</f>
         <v>1.455</v>
       </c>
-      <c r="Q30" s="21">
+      <c r="Q30" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262461.0)</f>
         <v>2262461</v>
       </c>
@@ -10876,12 +11053,12 @@
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="20">
+      <c r="G31" s="12"/>
+      <c r="H31" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9000000000000004)</f>
         <v>2.9</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -10906,11 +11083,11 @@
         <v>5</v>
       </c>
       <c r="O31" s="9"/>
-      <c r="P31" s="16">
+      <c r="P31" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.29)</f>
         <v>1.29</v>
       </c>
-      <c r="Q31" s="21">
+      <c r="Q31" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262450.0)</f>
         <v>2262450</v>
       </c>
@@ -10951,12 +11128,12 @@
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20">
+      <c r="G32" s="12"/>
+      <c r="H32" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1500000000000004)</f>
         <v>3.15</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.83)</f>
         <v>3.83</v>
       </c>
@@ -10981,11 +11158,11 @@
         <v>5</v>
       </c>
       <c r="O32" s="9"/>
-      <c r="P32" s="16">
+      <c r="P32" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.315)</f>
         <v>1.315</v>
       </c>
-      <c r="Q32" s="21">
+      <c r="Q32" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262523.0)</f>
         <v>2262523</v>
       </c>
@@ -11026,12 +11203,12 @@
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20">
+      <c r="G33" s="12"/>
+      <c r="H33" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
@@ -11056,11 +11233,11 @@
         <v>5</v>
       </c>
       <c r="O33" s="9"/>
-      <c r="P33" s="16">
+      <c r="P33" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.35)</f>
         <v>1.35</v>
       </c>
-      <c r="Q33" s="21">
+      <c r="Q33" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262533.0)</f>
         <v>2262533</v>
       </c>
@@ -11101,12 +11278,12 @@
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20">
+      <c r="G34" s="12"/>
+      <c r="H34" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.35)</f>
         <v>3.35</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
@@ -11131,11 +11308,11 @@
         <v>5</v>
       </c>
       <c r="O34" s="9"/>
-      <c r="P34" s="16">
+      <c r="P34" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.215)</f>
         <v>1.215</v>
       </c>
-      <c r="Q34" s="21">
+      <c r="Q34" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262441.0)</f>
         <v>2262441</v>
       </c>
@@ -11176,12 +11353,12 @@
       <c r="D35" s="11"/>
       <c r="E35" s="11"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="20">
+      <c r="G35" s="12"/>
+      <c r="H35" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5500000000000003)</f>
         <v>3.55</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
@@ -11206,11 +11383,11 @@
         <v>5</v>
       </c>
       <c r="O35" s="9"/>
-      <c r="P35" s="16">
+      <c r="P35" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2950000000000002)</f>
         <v>1.295</v>
       </c>
-      <c r="Q35" s="21">
+      <c r="Q35" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262875.0)</f>
         <v>2262875</v>
       </c>
@@ -11251,12 +11428,12 @@
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="20">
+      <c r="G36" s="12"/>
+      <c r="H36" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.67)</f>
         <v>4.67</v>
       </c>
@@ -11281,11 +11458,11 @@
         <v>5</v>
       </c>
       <c r="O36" s="9"/>
-      <c r="P36" s="16">
+      <c r="P36" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.21)</f>
         <v>1.21</v>
       </c>
-      <c r="Q36" s="21">
+      <c r="Q36" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2262415.0)</f>
         <v>2262415</v>
       </c>
@@ -11469,7 +11646,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
         <v>PQT</v>
       </c>
-      <c r="H1" s="7" t="str">
+      <c r="H1" s="5" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TUTOR")</f>
         <v>TUTOR</v>
       </c>
@@ -11526,11 +11703,11 @@
       <c r="D2" s="11"/>
       <c r="E2" s="11"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="H2" s="14"/>
+      <c r="G2" s="19">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H2" s="20"/>
       <c r="I2" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -11548,7 +11725,7 @@
         <v>2.2</v>
       </c>
       <c r="M2" s="9"/>
-      <c r="N2" s="16">
+      <c r="N2" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.25)</f>
         <v>1.25</v>
       </c>
@@ -11584,11 +11761,11 @@
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="12">
+      <c r="G3" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="H3" s="14"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
@@ -11606,7 +11783,7 @@
         <v>1.8</v>
       </c>
       <c r="M3" s="9"/>
-      <c r="N3" s="16">
+      <c r="N3" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.085)</f>
         <v>1.085</v>
       </c>
@@ -11642,11 +11819,11 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="12">
+      <c r="G4" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="H4" s="14"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -11664,7 +11841,7 @@
         <v>4.6</v>
       </c>
       <c r="M4" s="9"/>
-      <c r="N4" s="16">
+      <c r="N4" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.13)</f>
         <v>1.13</v>
       </c>
@@ -11700,11 +11877,11 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="12">
+      <c r="G5" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="H5" s="14"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
@@ -11722,7 +11899,7 @@
         <v>2.5</v>
       </c>
       <c r="M5" s="9"/>
-      <c r="N5" s="16">
+      <c r="N5" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
         <v>1.16</v>
       </c>
@@ -11758,11 +11935,11 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="12">
+      <c r="G6" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="H6" s="14"/>
+      <c r="H6" s="20"/>
       <c r="I6" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -11780,7 +11957,7 @@
         <v>4.6</v>
       </c>
       <c r="M6" s="9"/>
-      <c r="N6" s="16">
+      <c r="N6" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.95)</f>
         <v>0.95</v>
       </c>
@@ -11816,11 +11993,11 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="12">
+      <c r="G7" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="20"/>
       <c r="I7" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
@@ -11838,7 +12015,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="9"/>
-      <c r="N7" s="16">
+      <c r="N7" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5900000000000001)</f>
         <v>0.59</v>
       </c>
@@ -11874,11 +12051,11 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="12">
+      <c r="G8" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="20"/>
       <c r="I8" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -11896,7 +12073,7 @@
         <v>4.6</v>
       </c>
       <c r="M8" s="9"/>
-      <c r="N8" s="16">
+      <c r="N8" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.06)</f>
         <v>1.06</v>
       </c>
@@ -11932,11 +12109,11 @@
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="H9" s="14"/>
+      <c r="G9" s="19">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H9" s="20"/>
       <c r="I9" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -11954,7 +12131,7 @@
         <v>3.5</v>
       </c>
       <c r="M9" s="9"/>
-      <c r="N9" s="16">
+      <c r="N9" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.25)</f>
         <v>1.25</v>
       </c>
@@ -11990,11 +12167,11 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="12">
+      <c r="G10" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="H10" s="14"/>
+      <c r="H10" s="20"/>
       <c r="I10" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
@@ -12012,7 +12189,7 @@
         <v>4.6</v>
       </c>
       <c r="M10" s="9"/>
-      <c r="N10" s="16">
+      <c r="N10" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9550000000000001)</f>
         <v>0.955</v>
       </c>
@@ -12048,11 +12225,11 @@
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="12">
+      <c r="G11" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
       </c>
-      <c r="H11" s="14"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -12070,7 +12247,7 @@
         <v>3.1</v>
       </c>
       <c r="M11" s="9"/>
-      <c r="N11" s="16">
+      <c r="N11" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.79)</f>
         <v>0.79</v>
       </c>
@@ -12106,11 +12283,11 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12">
+      <c r="G12" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="H12" s="14"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -12125,7 +12302,7 @@
         <v>3.5</v>
       </c>
       <c r="M12" s="9"/>
-      <c r="N12" s="16">
+      <c r="N12" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.815)</f>
         <v>0.815</v>
       </c>
@@ -12161,11 +12338,11 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="12">
+      <c r="G13" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="H13" s="14"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -12183,7 +12360,7 @@
         <v>2.2</v>
       </c>
       <c r="M13" s="9"/>
-      <c r="N13" s="16">
+      <c r="N13" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
         <v>1.1</v>
       </c>
@@ -12219,11 +12396,11 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="12">
+      <c r="G14" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="H14" s="14"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -12241,7 +12418,7 @@
         <v>2.5</v>
       </c>
       <c r="M14" s="9"/>
-      <c r="N14" s="16">
+      <c r="N14" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.78)</f>
         <v>0.78</v>
       </c>
@@ -12277,11 +12454,11 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="12">
+      <c r="G15" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="H15" s="14"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -12299,7 +12476,7 @@
         <v>3.5</v>
       </c>
       <c r="M15" s="9"/>
-      <c r="N15" s="16">
+      <c r="N15" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.81)</f>
         <v>0.81</v>
       </c>
@@ -12335,11 +12512,11 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="12">
+      <c r="G16" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="H16" s="14"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -12357,7 +12534,7 @@
         <v>3.1</v>
       </c>
       <c r="M16" s="9"/>
-      <c r="N16" s="16">
+      <c r="N16" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.095)</f>
         <v>1.095</v>
       </c>
@@ -12393,11 +12570,11 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12">
+      <c r="G17" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="H17" s="14"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -12415,7 +12592,7 @@
         <v>4.6</v>
       </c>
       <c r="M17" s="9"/>
-      <c r="N17" s="16">
+      <c r="N17" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.04)</f>
         <v>1.04</v>
       </c>
@@ -12451,11 +12628,11 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12">
+      <c r="G18" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
       </c>
-      <c r="H18" s="14"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
@@ -12473,7 +12650,7 @@
         <v>3.1</v>
       </c>
       <c r="M18" s="9"/>
-      <c r="N18" s="16">
+      <c r="N18" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9500000000000001)</f>
         <v>0.95</v>
       </c>
@@ -12509,11 +12686,11 @@
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="12">
+      <c r="G19" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
       </c>
-      <c r="H19" s="14"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -12531,7 +12708,7 @@
         <v>4.6</v>
       </c>
       <c r="M19" s="9"/>
-      <c r="N19" s="16">
+      <c r="N19" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.105)</f>
         <v>1.105</v>
       </c>
@@ -12567,11 +12744,11 @@
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="12">
+      <c r="G20" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
-      <c r="H20" s="14"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -12589,7 +12766,7 @@
         <v>1.7</v>
       </c>
       <c r="M20" s="9"/>
-      <c r="N20" s="16">
+      <c r="N20" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.11)</f>
         <v>1.11</v>
       </c>
@@ -12625,11 +12802,11 @@
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="12">
+      <c r="G21" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
-      <c r="H21" s="14"/>
+      <c r="H21" s="20"/>
       <c r="I21" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
@@ -12647,7 +12824,7 @@
         <v>4.6</v>
       </c>
       <c r="M21" s="9"/>
-      <c r="N21" s="16">
+      <c r="N21" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.62)</f>
         <v>0.62</v>
       </c>
@@ -12683,11 +12860,11 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="12">
+      <c r="G22" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="H22" s="14"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
@@ -12705,7 +12882,7 @@
         <v>4.6</v>
       </c>
       <c r="M22" s="9"/>
-      <c r="N22" s="16">
+      <c r="N22" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.99)</f>
         <v>0.99</v>
       </c>
@@ -12741,11 +12918,11 @@
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="12">
+      <c r="G23" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="H23" s="14"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -12763,7 +12940,7 @@
         <v>3.1</v>
       </c>
       <c r="M23" s="9"/>
-      <c r="N23" s="16">
+      <c r="N23" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.83)</f>
         <v>0.83</v>
       </c>
@@ -12799,11 +12976,11 @@
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="12">
+      <c r="G24" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="H24" s="14"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
@@ -12821,7 +12998,7 @@
         <v>4.8</v>
       </c>
       <c r="M24" s="9"/>
-      <c r="N24" s="16">
+      <c r="N24" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.16)</f>
         <v>1.16</v>
       </c>
@@ -12857,11 +13034,11 @@
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="12">
+      <c r="G25" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="H25" s="14"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -12879,7 +13056,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="9"/>
-      <c r="N25" s="16">
+      <c r="N25" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.22)</f>
         <v>1.22</v>
       </c>
@@ -12915,11 +13092,11 @@
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="12">
+      <c r="G26" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="H26" s="14"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
@@ -12937,7 +13114,7 @@
         <v>4.3</v>
       </c>
       <c r="M26" s="9"/>
-      <c r="N26" s="16">
+      <c r="N26" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.98)</f>
         <v>0.98</v>
       </c>
@@ -12973,11 +13150,11 @@
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="12">
+      <c r="G27" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="H27" s="14"/>
+      <c r="H27" s="20"/>
       <c r="I27" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -12992,7 +13169,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="9"/>
-      <c r="N27" s="16">
+      <c r="N27" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2)</f>
         <v>0.2</v>
       </c>
@@ -13028,11 +13205,11 @@
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12">
+      <c r="G28" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="H28" s="14"/>
+      <c r="H28" s="20"/>
       <c r="I28" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -13050,7 +13227,7 @@
         <v>5</v>
       </c>
       <c r="M28" s="9"/>
-      <c r="N28" s="16">
+      <c r="N28" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.04)</f>
         <v>1.04</v>
       </c>
@@ -13079,18 +13256,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"UZCATEGUI GUILLEN ALEX MIGUEL")</f>
         <v>UZCATEGUI GUILLEN ALEX MIGUEL</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="23">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="12">
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="H29" s="14"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -13108,7 +13285,7 @@
         <v>3.1</v>
       </c>
       <c r="M29" s="10"/>
-      <c r="N29" s="16">
+      <c r="N29" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.115)</f>
         <v>1.115</v>
       </c>
@@ -13126,18 +13303,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLALOBOS ESPAÑA JULIAN ANDRES")</f>
         <v>VILLALOBOS ESPAÑA JULIAN ANDRES</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="23">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="12">
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="19">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="H30" s="14"/>
+      <c r="H30" s="20"/>
       <c r="I30" s="9">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -13155,7 +13332,7 @@
         <v>3.1</v>
       </c>
       <c r="M30" s="10"/>
-      <c r="N30" s="16">
+      <c r="N30" s="17">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.175)</f>
         <v>1.175</v>
       </c>
